--- a/ig/DM-JUIN-2025/ValueSet-JDV-J209-TypeSavoirFaire-ROR.xlsx
+++ b/ig/DM-JUIN-2025/ValueSet-JDV-J209-TypeSavoirFaire-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20231030120000</t>
+    <t>20250625120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-30T12:00:00+01:00</t>
+    <t>2025-06-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t>Compétence exclusive</t>
+  </si>
+  <si>
+    <t>CM</t>
+  </si>
+  <si>
+    <t>Compétence métier</t>
   </si>
   <si>
     <t>DEC</t>
@@ -433,7 +439,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -541,15 +547,23 @@
         <v>50</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>52</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
